--- a/backend/src/main/resources/templates/temple.xlsx
+++ b/backend/src/main/resources/templates/temple.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t xml:space="preserve">Issuer: {shipperCompany}
                                                                                  </t>
@@ -220,9 +220,6 @@
     <t>MEAS.</t>
   </si>
   <si>
-    <t>{products.quantity}</t>
-  </si>
-  <si>
     <t>{.cartons}</t>
   </si>
   <si>
@@ -262,7 +259,7 @@
     <t>CBM</t>
   </si>
   <si>
-    <t>TOTAL PACKED IN {totalQuantity} CARTONS</t>
+    <t>TOTAL PACKED IN  {totalCartons}  CARTONS</t>
   </si>
 </sst>
 </file>
@@ -512,16 +509,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <i/>
       <sz val="16"/>
       <name val="NSimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2167,7 +2164,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38.6296296296296" customWidth="1"/>
-    <col min="2" max="2" width="6.37962962962963" customWidth="1"/>
+    <col min="2" max="2" width="15.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="4.12962962962963" customWidth="1"/>
     <col min="4" max="4" width="4.62962962962963" customWidth="1"/>
     <col min="5" max="5" width="8.62962962962963" customWidth="1"/>
@@ -2323,34 +2320,34 @@
         <v>17</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="F9" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="G9" t="s">
         <v>42</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="I9" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="32" t="s">
+      <c r="K9" s="33" t="s">
         <v>45</v>
-      </c>
-      <c r="K9" s="33" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:16">
@@ -2429,33 +2426,33 @@
         <v>25</v>
       </c>
       <c r="D15" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="32" t="s">
+      <c r="G15" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="H15" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="I15" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="J15" s="32" t="s">
+      <c r="K15" s="33" t="s">
         <v>51</v>
-      </c>
-      <c r="K15" s="33" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="16" ht="21.95" customHeight="1" spans="1:16">
       <c r="A16" s="37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="38"/>
       <c r="C16" s="38"/>

--- a/backend/src/main/resources/templates/temple.xlsx
+++ b/backend/src/main/resources/templates/temple.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
   <si>
     <t xml:space="preserve">Issuer: {shipperCompany}
                                                                                  </t>
@@ -61,11 +61,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t>To:{consigneeCompany}</t>
     </r>
     <r>
@@ -189,6 +184,26 @@
         <charset val="134"/>
       </rPr>
       <t>PACKING LIST</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>To:{consigneeCompany}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+                                                                                          </t>
     </r>
   </si>
   <si>
@@ -2210,7 +2225,7 @@
     </row>
     <row r="3" ht="47.45" customHeight="1" spans="1:16">
       <c r="A3" s="6" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2235,7 +2250,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -2245,7 +2260,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>8</v>
@@ -2295,23 +2310,23 @@
         <v>11</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I8" s="28"/>
       <c r="J8" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K8" s="28"/>
     </row>
@@ -2326,28 +2341,28 @@
         <v>19</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="I9" s="31" t="s">
-        <v>42</v>
-      </c>
       <c r="J9" s="32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:16">
@@ -2426,33 +2441,33 @@
         <v>25</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="31" t="s">
-        <v>48</v>
-      </c>
       <c r="J15" s="32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K15" s="33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" ht="21.95" customHeight="1" spans="1:16">
       <c r="A16" s="37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="38"/>
       <c r="C16" s="38"/>

--- a/backend/src/main/resources/templates/temple.xlsx
+++ b/backend/src/main/resources/templates/temple.xlsx
@@ -61,6 +61,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>To:{consigneeCompany}</t>
     </r>
     <r>
@@ -90,7 +95,7 @@
     <t>Terms of payment  T/T</t>
   </si>
   <si>
-    <t>From  SHANGHAI, CHINA</t>
+    <t>From  {departureCityEnglish}, CHINA</t>
   </si>
   <si>
     <t>To      {destinationRegion}</t>
@@ -158,7 +163,7 @@
     <t>{totalAmountWords}</t>
   </si>
   <si>
-    <t>TOTAL PACKED IN {totalCartons} CARTONS</t>
+    <t>TOTAL PACKED IN {totalCartons} {contonEN}</t>
   </si>
   <si>
     <t>N/M</t>
@@ -187,26 +192,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>To:{consigneeCompany}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-                                                                                          </t>
-    </r>
-  </si>
-  <si>
     <t>Date:  {date}</t>
   </si>
   <si>
@@ -238,7 +223,7 @@
     <t>{.cartons}</t>
   </si>
   <si>
-    <t>CARTONS</t>
+    <t>{.contonEN}</t>
   </si>
   <si>
     <t>{.grossWeight}</t>
@@ -259,6 +244,9 @@
     <t>{totalCartons}</t>
   </si>
   <si>
+    <t>{contonEN}</t>
+  </si>
+  <si>
     <t>{totalGrossWeight}</t>
   </si>
   <si>
@@ -274,7 +262,7 @@
     <t>CBM</t>
   </si>
   <si>
-    <t>TOTAL PACKED IN  {totalCartons}  CARTONS</t>
+    <t>TOTAL PACKED IN  {totalCartons}  {contonEN}</t>
   </si>
 </sst>
 </file>
@@ -524,16 +512,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <sz val="16"/>
       <name val="NSimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2225,7 +2213,7 @@
     </row>
     <row r="3" ht="47.45" customHeight="1" spans="1:16">
       <c r="A3" s="6" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2250,7 +2238,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -2260,7 +2248,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>8</v>
@@ -2310,23 +2298,23 @@
         <v>11</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" s="28"/>
       <c r="J8" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K8" s="28"/>
     </row>
@@ -2341,28 +2329,28 @@
         <v>19</v>
       </c>
       <c r="D9" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="F9" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="G9" t="s">
         <v>42</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="I9" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="32" t="s">
+      <c r="K9" s="33" t="s">
         <v>45</v>
-      </c>
-      <c r="K9" s="33" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:16">
@@ -2441,10 +2429,10 @@
         <v>25</v>
       </c>
       <c r="D15" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="31" t="s">
         <v>47</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>41</v>
       </c>
       <c r="F15" s="32" t="s">
         <v>48</v>

--- a/backend/src/main/resources/templates/temple.xlsx
+++ b/backend/src/main/resources/templates/temple.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="CI" sheetId="30" r:id="rId1"/>
@@ -92,7 +92,7 @@
     <t>Transport details              {transportMode}</t>
   </si>
   <si>
-    <t>Terms of payment  T/T</t>
+    <t>Terms of payment  {paymentMethod}</t>
   </si>
   <si>
     <t>From  {departureCityEnglish}, CHINA</t>
@@ -512,16 +512,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <i/>
       <sz val="16"/>
       <name val="NSimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>

--- a/backend/src/main/resources/templates/temple.xlsx
+++ b/backend/src/main/resources/templates/temple.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="CI" sheetId="30" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t xml:space="preserve">Issuer: {shipperCompany}
                                                                                  </t>
@@ -146,12 +146,6 @@
   </si>
   <si>
     <t xml:space="preserve">      TOTAL:</t>
-  </si>
-  <si>
-    <t>{totalQuantity}</t>
-  </si>
-  <si>
-    <t>PCS</t>
   </si>
   <si>
     <t>{currency}</t>
@@ -1982,24 +1976,20 @@
       <c r="A17" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="66" t="s">
-        <v>25</v>
-      </c>
+      <c r="B17" s="65"/>
+      <c r="C17" s="66"/>
       <c r="D17" s="59"/>
       <c r="E17" s="59"/>
       <c r="F17" s="65" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G17" s="67" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" ht="21.95" customHeight="1" spans="1:7">
       <c r="A18" s="68" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18" s="62"/>
       <c r="C18" s="62"/>
@@ -2010,7 +2000,7 @@
     </row>
     <row r="19" ht="21.95" customHeight="1" spans="1:7">
       <c r="A19" s="68" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19" s="62"/>
       <c r="C19" s="62"/>
@@ -2021,7 +2011,7 @@
     </row>
     <row r="20" ht="21.95" customHeight="1" spans="1:7">
       <c r="A20" s="40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
@@ -2184,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -2238,7 +2228,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="11"/>
       <c r="F4" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -2248,7 +2238,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>8</v>
@@ -2298,23 +2288,23 @@
         <v>11</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I8" s="28"/>
       <c r="J8" s="27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K8" s="28"/>
     </row>
@@ -2329,28 +2319,28 @@
         <v>19</v>
       </c>
       <c r="D9" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="G9" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="H9" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="K9" s="33" t="s">
         <v>43</v>
-      </c>
-      <c r="I9" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="33" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10" ht="21.95" customHeight="1" spans="1:16">
@@ -2422,40 +2412,36 @@
       <c r="A15" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>25</v>
-      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
       <c r="D15" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="G15" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="H15" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="I15" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="K15" s="33" t="s">
         <v>50</v>
-      </c>
-      <c r="I15" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="K15" s="33" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="16" ht="21.95" customHeight="1" spans="1:16">
       <c r="A16" s="37" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B16" s="38"/>
       <c r="C16" s="38"/>
@@ -2470,7 +2456,7 @@
     </row>
     <row r="17" ht="21.95" customHeight="1" spans="1:11">
       <c r="A17" s="40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="41"/>
